--- a/artfynd/A 27590-2026 artfynd.xlsx
+++ b/artfynd/A 27590-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75247505</v>
+        <v>135476484</v>
       </c>
       <c r="B2" t="n">
-        <v>93213</v>
+        <v>90997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tärnickflon, mellan myren och Ångermanälven, Ång</t>
+          <t>Bpmmeråskullen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601514</v>
+        <v>601661</v>
       </c>
       <c r="R2" t="n">
-        <v>7071922</v>
+        <v>7071904</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,42 +757,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>olikåldrig, gallrad tallskog med enstaka gamla tallar, på torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>bland väggmossa, ljung och lingon</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75247506</v>
+        <v>75247505</v>
       </c>
       <c r="B3" t="n">
-        <v>90691</v>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601408</v>
+        <v>601514</v>
       </c>
       <c r="R3" t="n">
-        <v>7071945</v>
+        <v>7071922</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -888,12 +869,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>gammal, olikåldrig tallskog, på torr moränmark</t>
+          <t>olikåldrig, gallrad tallskog med enstaka gamla tallar, på torr moränmark</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>bland väggmossa och lingon</t>
+          <t>bland väggmossa, ljung och lingon</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -908,6 +889,126 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>75247506</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tärnickflon, mellan myren och Ångermanälven, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>601408</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7071945</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-09-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-09-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>gammal, olikåldrig tallskog, på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>bland väggmossa och lingon</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 27590-2026 artfynd.xlsx
+++ b/artfynd/A 27590-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135476484</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247505</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,8 +1028,18 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247506</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27590-2026 artfynd.xlsx
+++ b/artfynd/A 27590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135476484</v>
       </c>
       <c r="B2" t="n">
-        <v>90997</v>
+        <v>91039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27590-2026 artfynd.xlsx
+++ b/artfynd/A 27590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135476484</v>
       </c>
       <c r="B2" t="n">
-        <v>91039</v>
+        <v>91066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27590-2026 artfynd.xlsx
+++ b/artfynd/A 27590-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,54 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75247505</v>
+        <v>135476484</v>
       </c>
       <c r="B2" t="n">
-        <v>93213</v>
+        <v>91069</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tärnickflon, mellan myren och Ångermanälven, Ång</t>
+          <t>Bpmmeråskullen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601514</v>
+        <v>601661</v>
       </c>
       <c r="R2" t="n">
-        <v>7071922</v>
+        <v>7071904</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,47 +762,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>olikåldrig, gallrad tallskog med enstaka gamla tallar, på torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>bland väggmossa, ljung och lingon</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Mattias Edman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Mattias Edman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75247505</t>
+          <t>https://artportalen.se/Sighting/135476484</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75247506</v>
+        <v>75247505</v>
       </c>
       <c r="B3" t="n">
-        <v>90691</v>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601408</v>
+        <v>601514</v>
       </c>
       <c r="R3" t="n">
-        <v>7071945</v>
+        <v>7071922</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -898,12 +879,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>gammal, olikåldrig tallskog, på torr moränmark</t>
+          <t>olikåldrig, gallrad tallskog med enstaka gamla tallar, på torr moränmark</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>bland väggmossa och lingon</t>
+          <t>bland väggmossa, ljung och lingon</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -923,6 +904,131 @@
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247505</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>75247506</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tärnickflon, mellan myren och Ångermanälven, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>601408</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7071945</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-09-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-09-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>gammal, olikåldrig tallskog, på torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>bland väggmossa och lingon</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/75247506</t>
         </is>
@@ -932,6 +1038,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27590-2026 artfynd.xlsx
+++ b/artfynd/A 27590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135476484</v>
       </c>
       <c r="B2" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27590-2026 artfynd.xlsx
+++ b/artfynd/A 27590-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135476484</v>
       </c>
       <c r="B2" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
